--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Mott's Wrecker Service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE5B4848-C1A3-4F7C-937D-2FE89D6FEE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05036CF9-DB45-4B94-A1C9-EF54263859DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23295" windowHeight="13380" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Mott's Wrecker Service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05036CF9-DB45-4B94-A1C9-EF54263859DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF1BCB4-5356-4F56-A5C6-38BBF1558B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1383,7 +1383,7 @@
         <v>46091.544560185182</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF1BCB4-5356-4F56-A5C6-38BBF1558B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C46C49D-45B7-4CDC-94DB-4A1E818EC982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C46C49D-45B7-4CDC-94DB-4A1E818EC982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4106A4-F800-4FB8-A47F-8CE5F962D9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="33">
   <si>
     <t>Company Name</t>
   </si>
@@ -126,6 +126,18 @@
   </si>
   <si>
     <t>Jacky Clay Messer</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Mark Franklin</t>
+  </si>
+  <si>
+    <t>INCOMPLETE</t>
+  </si>
+  <si>
+    <t>Mark Complete</t>
   </si>
 </sst>
 </file>
@@ -1390,82 +1402,188 @@
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H29" s="2"/>
-      <c r="I29" s="1"/>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29">
+        <v>5042</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="2">
+        <v>8.4606481481481477E-3</v>
+      </c>
+      <c r="I29" s="1">
+        <v>46118.794675925928</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H30" s="2"/>
-      <c r="I30" s="1"/>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30">
+        <v>5304</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="2">
+        <v>2.0949074074074073E-3</v>
+      </c>
+      <c r="I30" s="1">
+        <v>46118.795370370368</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H31" s="2"/>
-      <c r="I31" s="1"/>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <v>5040</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>46118.796064814815</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H32" s="2"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32">
+        <v>5403</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>46118.796064814815</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H33" s="2"/>
       <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H35" s="2"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H39" s="2"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H40" s="2"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H41" s="2"/>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H42" s="2"/>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H43" s="2"/>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H44" s="2"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H45" s="2"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H46" s="2"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H47" s="2"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H48" s="2"/>
       <c r="I48" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4106A4-F800-4FB8-A47F-8CE5F962D9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC770695-05AE-482A-906B-FCACEDF2C4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="33">
   <si>
     <t>Company Name</t>
   </si>
@@ -1476,114 +1476,117 @@
         <v>29</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
+        <v>7.362268518518518E-2</v>
       </c>
       <c r="I31" s="1">
         <v>46118.796064814815</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
+      <c r="H32" s="2"/>
+      <c r="I32" s="1"/>
+      <c r="K32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>19</v>
       </c>
-      <c r="C32">
+      <c r="C33">
         <v>5403</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>30</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F33" t="s">
         <v>29</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G33" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H33" s="2">
         <v>0</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I33" s="1">
         <v>46118.796064814815</v>
       </c>
-      <c r="J32">
+      <c r="J33">
         <v>0</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H33" s="2"/>
-      <c r="I33" s="1"/>
-      <c r="K33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H35" s="2"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H39" s="2"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H40" s="2"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H41" s="2"/>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H42" s="2"/>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H43" s="2"/>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H44" s="2"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H45" s="2"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H46" s="2"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H47" s="2"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H48" s="2"/>
       <c r="I48" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC770695-05AE-482A-906B-FCACEDF2C4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B105FC-9605-4C9F-932F-B66AAC4F32B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B105FC-9605-4C9F-932F-B66AAC4F32B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D842A03-CF87-4EA9-B3A9-A4D616B08348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="33">
   <si>
     <t>Company Name</t>
   </si>
@@ -1535,24 +1535,130 @@
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H35" s="2"/>
-      <c r="I35" s="1"/>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35">
+        <v>5042</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="2">
+        <v>4.7106481481481478E-3</v>
+      </c>
+      <c r="I35" s="1">
+        <v>46146.685185185182</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H36" s="2"/>
-      <c r="I36" s="1"/>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36">
+        <v>5304</v>
+      </c>
+      <c r="D36" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="2">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="I36" s="1">
+        <v>46146.685879629629</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
+      <c r="K37" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38">
+        <v>5040</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>46146.686574074076</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39">
+        <v>5403</v>
+      </c>
+      <c r="D39" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="2">
+        <v>7.2569444444444443E-3</v>
+      </c>
+      <c r="I39" s="1">
+        <v>46146.686574074076</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H40" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D842A03-CF87-4EA9-B3A9-A4D616B08348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330BAF64-0B32-4AEE-9E49-8C97DB1FD374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="33">
   <si>
     <t>Company Name</t>
   </si>
@@ -1580,10 +1580,10 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H36" s="2">
-        <v>2.8935185185185184E-4</v>
+        <v>6.8402777777777776E-3</v>
       </c>
       <c r="I36" s="1">
         <v>46146.685879629629</v>
@@ -1596,10 +1596,32 @@
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37">
+        <v>5040</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>46146.686574074076</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
       <c r="K37" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
@@ -1607,19 +1629,19 @@
         <v>19</v>
       </c>
       <c r="C38">
-        <v>5040</v>
+        <v>5403</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
+        <v>7.2569444444444443E-3</v>
       </c>
       <c r="I38" s="1">
         <v>46146.686574074076</v>
@@ -1632,33 +1654,8 @@
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39">
-        <v>5403</v>
-      </c>
-      <c r="D39" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H39" s="2">
-        <v>7.2569444444444443E-3</v>
-      </c>
-      <c r="I39" s="1">
-        <v>46146.686574074076</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39" t="s">
-        <v>11</v>
-      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="1"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H40" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3D5EF9-93CF-484C-B4D9-1CED6553E318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC7A563-B0BF-4E9D-8C40-08C574273661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott's Wrecker Service- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4256705-BACA-42B3-9585-0FEE49A8FF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B25973-D5B3-40BB-8215-9C005D6069A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1740,16 +1740,16 @@
         <v>24</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H41" s="2">
-        <v>0</v>
+        <v>9.780092592592592E-3</v>
       </c>
       <c r="I41" s="1">
         <v>46176.473611111112</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFD98C2F-22B6-4D54-9946-A7A1333C7D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7675CAA0-3C62-401F-84BE-AE9198B7F4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -119,6 +119,9 @@
     <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
+    <t>3 Points of Contact</t>
+  </si>
+  <si>
     <t>Mott's Wrecker Service</t>
   </si>
   <si>
@@ -135,9 +138,6 @@
   </si>
   <si>
     <t>Frank Almendarez III</t>
-  </si>
-  <si>
-    <t>3 Points of Contact</t>
   </si>
   <si>
     <t>Jacky Clay Messer</t>
@@ -517,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -566,16 +566,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>4898</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>19</v>
@@ -598,16 +598,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
         <v>4898</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -630,16 +630,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>4898</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
@@ -662,16 +662,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5">
         <v>5041</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>17</v>
@@ -694,16 +694,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>5042</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
@@ -726,16 +726,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>4898</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>16</v>
@@ -758,13 +758,13 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8">
         <v>5040</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>16</v>
@@ -787,16 +787,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9">
         <v>5041</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>16</v>
@@ -819,16 +819,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10">
         <v>5042</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>22</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11">
         <v>4898</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>22</v>
@@ -883,13 +883,13 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12">
         <v>5040</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>22</v>
@@ -912,16 +912,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13">
         <v>5041</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>22</v>
@@ -944,16 +944,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14">
         <v>5042</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>25</v>
@@ -976,16 +976,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15">
         <v>5043</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>25</v>
@@ -1008,13 +1008,13 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16">
         <v>5040</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>25</v>
@@ -1037,16 +1037,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17">
         <v>5041</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>25</v>
@@ -1069,16 +1069,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18">
         <v>5042</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>25</v>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19">
         <v>5043</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>25</v>
@@ -1133,13 +1133,13 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20">
         <v>5040</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>25</v>
@@ -1162,19 +1162,19 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21">
         <v>5042</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1194,19 +1194,19 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E22">
         <v>5043</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1226,16 +1226,16 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E23">
         <v>5040</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1255,19 +1255,19 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24">
         <v>5041</v>
       </c>
       <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
         <v>29</v>
       </c>
-      <c r="G24" t="s">
-        <v>28</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1287,16 +1287,16 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25">
         <v>5042</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>20</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26">
         <v>5304</v>
@@ -1348,13 +1348,13 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27">
         <v>5040</v>
       </c>
       <c r="F27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>20</v>
@@ -1377,16 +1377,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28">
         <v>5041</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>20</v>
@@ -1409,16 +1409,16 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E29">
         <v>5042</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>23</v>
@@ -1441,7 +1441,7 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E30">
         <v>5304</v>
@@ -1470,13 +1470,13 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E31">
         <v>5040</v>
       </c>
       <c r="F31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>23</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E33">
         <v>5403</v>
@@ -1546,16 +1546,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35">
         <v>5042</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>17</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36">
         <v>5304</v>
@@ -1607,13 +1607,13 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E37">
         <v>5040</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>17</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E38">
         <v>5403</v>
@@ -1665,16 +1665,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E39">
         <v>5042</v>
       </c>
       <c r="F39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>14</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E40">
         <v>5403</v>
@@ -1726,16 +1726,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E41">
         <v>5042</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>24</v>
@@ -6266,6 +6266,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -39917,7 +39918,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7675CAA0-3C62-401F-84BE-AE9198B7F4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A83C0C65-F083-4562-9F9C-10FB04082044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="37">
   <si>
     <t>Company Name</t>
   </si>
@@ -83,7 +83,10 @@
     <t>PENDING</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -95,19 +98,22 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Alert Driving</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
+    <t>Speed Management</t>
   </si>
   <si>
-    <t>Mark Complete</t>
+    <t>Space Management-Big 5</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
@@ -116,10 +122,10 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Camera Event Management Orientation for Drivers</t>
+    <t>3 Points of Contact</t>
   </si>
   <si>
-    <t>3 Points of Contact</t>
+    <t>Jacob Fortes</t>
   </si>
   <si>
     <t>Mott's Wrecker Service</t>
@@ -517,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -566,19 +572,19 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>4898</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -598,19 +604,19 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>4898</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -630,19 +636,19 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>4898</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -662,19 +668,19 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>5041</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -694,19 +700,19 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>5042</v>
       </c>
       <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -726,19 +732,19 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>4898</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -758,16 +764,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>5040</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -787,19 +793,19 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>5041</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -819,19 +825,19 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10">
         <v>5042</v>
       </c>
       <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
         <v>31</v>
       </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -851,19 +857,19 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>4898</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -883,16 +889,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>5040</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -912,19 +918,19 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <v>5041</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -944,19 +950,19 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <v>5042</v>
       </c>
       <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
         <v>31</v>
       </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -976,19 +982,19 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E15">
         <v>5043</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1008,16 +1014,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16">
         <v>5040</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1037,19 +1043,19 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E17">
         <v>5041</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1069,19 +1075,19 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18">
         <v>5042</v>
       </c>
       <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
         <v>31</v>
       </c>
-      <c r="G18" t="s">
-        <v>29</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1101,19 +1107,19 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E19">
         <v>5043</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1133,16 +1139,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E20">
         <v>5040</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1162,19 +1168,19 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E21">
         <v>5042</v>
       </c>
       <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
         <v>31</v>
       </c>
-      <c r="G21" t="s">
-        <v>29</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1194,19 +1200,19 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E22">
         <v>5043</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1226,16 +1232,16 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E23">
         <v>5040</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1255,19 +1261,19 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E24">
         <v>5041</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1287,19 +1293,19 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E25">
         <v>5042</v>
       </c>
       <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
         <v>31</v>
       </c>
-      <c r="G25" t="s">
-        <v>29</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1319,16 +1325,16 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E26">
         <v>5304</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1348,16 +1354,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E27">
         <v>5040</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1377,19 +1383,19 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E28">
         <v>5041</v>
       </c>
       <c r="F28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -1409,19 +1415,19 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E29">
         <v>5042</v>
       </c>
       <c r="F29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" t="s">
         <v>31</v>
       </c>
-      <c r="G29" t="s">
-        <v>29</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1441,16 +1447,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E30">
         <v>5304</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1470,16 +1476,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E31">
         <v>5040</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>12</v>
@@ -1503,21 +1509,21 @@
       <c r="J32" s="2"/>
       <c r="K32" s="1"/>
       <c r="M32" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E33">
         <v>5403</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>12</v>
@@ -1541,24 +1547,24 @@
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
       <c r="M34" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E35">
         <v>5042</v>
       </c>
       <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
         <v>31</v>
       </c>
-      <c r="G35" t="s">
-        <v>29</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1578,16 +1584,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E36">
         <v>5304</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1607,16 +1613,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E37">
         <v>5040</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1636,16 +1642,16 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E38">
         <v>5403</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1665,19 +1671,19 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E39">
         <v>5042</v>
       </c>
       <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
         <v>31</v>
       </c>
-      <c r="G39" t="s">
-        <v>29</v>
-      </c>
       <c r="H39" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1697,16 +1703,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E40">
         <v>5403</v>
       </c>
       <c r="F40" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1726,19 +1732,19 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E41">
         <v>5042</v>
       </c>
       <c r="F41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
         <v>31</v>
       </c>
-      <c r="G41" t="s">
-        <v>29</v>
-      </c>
       <c r="H41" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1757,34 +1763,135 @@
       </c>
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H42" s="2"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="1"/>
+      <c r="D42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42">
+        <v>5042</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J42" s="2">
+        <v>5.9375000000000001E-3</v>
+      </c>
+      <c r="K42" s="1">
+        <v>46219.630208333336</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H43" s="2"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="1"/>
+      <c r="D43" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43">
+        <v>5893</v>
+      </c>
+      <c r="F43" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43" s="2">
+        <v>3.6111111111111109E-3</v>
+      </c>
+      <c r="K43" s="1">
+        <v>46219.630902777775</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H44" s="2"/>
       <c r="I44" s="1"/>
       <c r="J44" s="2"/>
       <c r="K44" s="1"/>
+      <c r="M44" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H45" s="2"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="1"/>
+      <c r="D45" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45">
+        <v>5040</v>
+      </c>
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>46219.631597222222</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H46" s="2"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="1"/>
+      <c r="D46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46">
+        <v>5403</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J46" s="2">
+        <v>6.4699074074074077E-3</v>
+      </c>
+      <c r="K46" s="1">
+        <v>46219.631597222222</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H47" s="2"/>
@@ -6195,6 +6302,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -6290,6 +6398,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -6313,6 +6422,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -6576,6 +6686,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -6587,6 +6698,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -6598,6 +6710,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -7213,6 +7326,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -7337,6 +7451,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -7479,6 +7594,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -7508,6 +7624,7 @@
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -7578,6 +7695,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -7601,6 +7719,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -7665,6 +7784,7 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
@@ -7718,6 +7838,7 @@
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -7885,6 +8006,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -7896,6 +8018,7 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
@@ -7907,6 +8030,7 @@
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -7942,6 +8066,7 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
@@ -8091,6 +8216,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -8338,6 +8464,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -8396,6 +8523,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -8454,6 +8582,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -8465,6 +8594,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -8530,6 +8660,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -8565,6 +8696,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -8630,6 +8762,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -8676,6 +8809,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -8735,6 +8869,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -8793,6 +8928,7 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
@@ -8857,6 +8993,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -8939,6 +9076,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -9002,6 +9140,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -9017,6 +9156,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -9052,6 +9192,7 @@
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -9317,6 +9458,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -9600,6 +9742,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -9617,6 +9760,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -9640,6 +9784,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -9657,6 +9802,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -9989,6 +10135,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -10077,6 +10224,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -10170,6 +10318,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -10229,11 +10378,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -10285,6 +10436,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -10326,6 +10478,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -10370,6 +10523,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -10416,11 +10570,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -10618,6 +10774,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -10647,6 +10804,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -10662,6 +10821,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -10721,6 +10881,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -10792,6 +10953,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -10833,6 +10995,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -10951,6 +11114,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -11015,6 +11179,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -11139,6 +11304,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -11365,6 +11531,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -11482,6 +11649,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -11565,6 +11733,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -11624,6 +11793,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -11647,6 +11817,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -11694,6 +11865,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -11753,6 +11925,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -11776,6 +11949,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -11793,6 +11967,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -11876,6 +12051,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -12067,6 +12243,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -39923,6 +40100,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -39930,6 +40108,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -39937,6 +40116,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -39952,6 +40132,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -39961,6 +40142,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -39968,9 +40150,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -39978,12 +40166,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -39991,12 +40182,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -40008,9 +40202,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -40025,6 +40221,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -40051,6 +40248,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -40061,7 +40259,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -40069,6 +40272,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -40080,6 +40284,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -40087,6 +40292,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -40101,13 +40307,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -40118,15 +40330,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -40142,6 +40357,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -40160,6 +40376,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -40171,6 +40388,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -40188,18 +40406,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -40228,6 +40451,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -40235,9 +40459,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -40260,12 +40486,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -40280,9 +40509,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -40298,12 +40529,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -40324,6 +40557,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -40335,9 +40569,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -40349,6 +40585,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -40388,9 +40625,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -40398,9 +40637,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -40411,6 +40652,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -40418,18 +40660,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -40437,6 +40687,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -40447,6 +40698,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -40473,15 +40725,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -40503,6 +40759,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -40510,9 +40767,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -40520,6 +40779,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -40531,6 +40791,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -40545,6 +40806,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -40554,6 +40819,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -40565,6 +40831,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -40575,10 +40842,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -40586,6 +40858,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -40600,6 +40873,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -40622,6 +40896,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -40641,25 +40916,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -40667,6 +40954,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -40674,15 +40962,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -40696,6 +40991,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -40714,9 +41010,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -40724,9 +41022,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -40734,6 +41034,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -40750,10 +41051,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{072FE70B-8C24-4CE0-AFF5-0F77F9C02C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{911E5ED7-BD2D-45D7-8DC4-2B0949C7DCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="38">
   <si>
     <t>Company Name</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>Speed Mangement-C</t>
+  </si>
+  <si>
+    <t>Dangers of Distracted Driving</t>
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
@@ -523,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -538,50 +541,50 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>4898</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
@@ -602,18 +605,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>4898</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -634,18 +637,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>4898</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
@@ -666,18 +669,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>5041</v>
       </c>
       <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
         <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -698,18 +701,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>5042</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -730,18 +733,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>4898</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -762,15 +765,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>5040</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -791,18 +794,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>5041</v>
       </c>
       <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -823,18 +826,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>5042</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
@@ -855,18 +858,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>4898</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
@@ -887,15 +890,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>5040</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
@@ -916,18 +919,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>5041</v>
       </c>
       <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
         <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
@@ -948,21 +951,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>5042</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
         <v>10</v>
@@ -980,21 +983,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>5043</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
         <v>10</v>
@@ -1012,18 +1015,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>5040</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
         <v>10</v>
@@ -1043,19 +1046,19 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>5041</v>
       </c>
       <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" t="s">
         <v>32</v>
       </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
         <v>10</v>
@@ -1075,19 +1078,19 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18">
         <v>5042</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
         <v>10</v>
@@ -1107,19 +1110,19 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19">
         <v>5043</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
         <v>10</v>
@@ -1139,16 +1142,16 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20">
         <v>5040</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
@@ -1168,19 +1171,19 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21">
         <v>5042</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
         <v>10</v>
@@ -1200,19 +1203,19 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>5043</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
         <v>10</v>
@@ -1232,16 +1235,16 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23">
         <v>5040</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
@@ -1261,19 +1264,19 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24">
         <v>5041</v>
       </c>
       <c r="D24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
@@ -1293,16 +1296,16 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>5042</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
         <v>23</v>
@@ -1325,13 +1328,13 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26">
         <v>5304</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
         <v>23</v>
@@ -1354,13 +1357,13 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27">
         <v>5040</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
         <v>23</v>
@@ -1383,16 +1386,16 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>5041</v>
       </c>
       <c r="D28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" t="s">
         <v>32</v>
-      </c>
-      <c r="E28" t="s">
-        <v>31</v>
       </c>
       <c r="F28" t="s">
         <v>23</v>
@@ -1415,16 +1418,16 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C29">
         <v>5042</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
         <v>24</v>
@@ -1447,13 +1450,13 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30">
         <v>5304</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
         <v>24</v>
@@ -1476,13 +1479,13 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C31">
         <v>5040</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
         <v>24</v>
@@ -1513,13 +1516,13 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33">
         <v>5403</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
         <v>24</v>
@@ -1550,16 +1553,16 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C35">
         <v>5042</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
         <v>17</v>
@@ -1582,13 +1585,13 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C36">
         <v>5304</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
@@ -1611,13 +1614,13 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37">
         <v>5040</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
         <v>17</v>
@@ -1640,13 +1643,13 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38">
         <v>5403</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
@@ -1669,16 +1672,16 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39">
         <v>5042</v>
       </c>
       <c r="D39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
         <v>20</v>
@@ -1701,13 +1704,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40">
         <v>5403</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
@@ -1730,16 +1733,16 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41">
         <v>5042</v>
       </c>
       <c r="D41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -1762,16 +1765,16 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C42">
         <v>5042</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -1794,25 +1797,25 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C43">
         <v>5893</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H43" s="2">
-        <v>3.6111111111111109E-3</v>
+        <v>9.0624999999999994E-3</v>
       </c>
       <c r="I43" s="1">
         <v>46219.630902777775</v>
@@ -1825,22 +1828,43 @@
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H44" s="2"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="2"/>
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44">
+        <v>5040</v>
+      </c>
+      <c r="D44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="2">
+        <v>5.9953703703703705E-3</v>
+      </c>
+      <c r="I44" s="1">
+        <v>46219.631597222222</v>
+      </c>
+      <c r="J44" s="2">
+        <v>1</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C45">
-        <v>5040</v>
+        <v>5403</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -1849,13 +1873,13 @@
         <v>10</v>
       </c>
       <c r="H45" s="2">
-        <v>5.9953703703703705E-3</v>
+        <v>6.4699074074074077E-3</v>
       </c>
       <c r="I45" s="1">
         <v>46219.631597222222</v>
       </c>
       <c r="J45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>11</v>
@@ -1863,25 +1887,28 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C46">
-        <v>5403</v>
+        <v>5042</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
       </c>
       <c r="H46" s="2">
-        <v>6.4699074074074077E-3</v>
+        <v>6.053240740740741E-3</v>
       </c>
       <c r="I46" s="1">
-        <v>46219.631597222222</v>
+        <v>46237.814236111109</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
@@ -1891,108 +1918,180 @@
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H47" s="2"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="1"/>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47">
+        <v>5893</v>
+      </c>
+      <c r="D47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="2">
+        <v>8.2638888888888883E-3</v>
+      </c>
+      <c r="I47" s="1">
+        <v>46237.814930555556</v>
+      </c>
+      <c r="J47" s="2">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H48" s="2"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H49" s="2"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="1"/>
-    </row>
-    <row r="50" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48">
+        <v>5040</v>
+      </c>
+      <c r="D48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>46237.814930555556</v>
+      </c>
+      <c r="J48" s="2">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49">
+        <v>5403</v>
+      </c>
+      <c r="D49" t="s">
+        <v>37</v>
+      </c>
+      <c r="F49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" s="2">
+        <v>9.780092592592592E-3</v>
+      </c>
+      <c r="I49" s="1">
+        <v>46237.815625000003</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H50" s="2"/>
       <c r="I50" s="1"/>
       <c r="J50" s="2"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H51" s="2"/>
       <c r="I51" s="1"/>
       <c r="J51" s="2"/>
       <c r="K51" s="1"/>
     </row>
-    <row r="52" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H52" s="2"/>
       <c r="I52" s="1"/>
       <c r="J52" s="2"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H53" s="2"/>
       <c r="I53" s="1"/>
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
     </row>
-    <row r="54" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H54" s="2"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
       <c r="K54" s="1"/>
     </row>
-    <row r="55" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H55" s="2"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2"/>
       <c r="K55" s="1"/>
     </row>
-    <row r="56" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H56" s="2"/>
       <c r="I56" s="1"/>
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
     </row>
-    <row r="57" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H57" s="2"/>
       <c r="I57" s="1"/>
       <c r="J57" s="2"/>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H58" s="2"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2"/>
       <c r="K58" s="1"/>
     </row>
-    <row r="59" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H59" s="2"/>
       <c r="I59" s="1"/>
       <c r="J59" s="2"/>
       <c r="K59" s="1"/>
     </row>
-    <row r="60" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H60" s="2"/>
       <c r="I60" s="1"/>
       <c r="J60" s="2"/>
       <c r="K60" s="1"/>
     </row>
-    <row r="61" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H61" s="2"/>
       <c r="I61" s="1"/>
       <c r="J61" s="2"/>
       <c r="K61" s="1"/>
     </row>
-    <row r="62" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H62" s="2"/>
       <c r="I62" s="1"/>
       <c r="J62" s="2"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H63" s="2"/>
       <c r="I63" s="1"/>
       <c r="J63" s="2"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H64" s="2"/>
       <c r="I64" s="1"/>
       <c r="J64" s="2"/>
@@ -43742,6 +43841,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -43756,11 +43856,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -43771,10 +43873,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -43792,14 +43897,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -43810,14 +43918,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -43844,6 +43955,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -43852,6 +43964,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -43864,22 +43977,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -43898,6 +44016,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -43908,10 +44027,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -43920,10 +44041,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -43937,82 +44060,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -44026,6 +44164,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44036,6 +44175,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -44043,6 +44183,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -44051,86 +44192,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44147,26 +44301,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -44197,6 +44357,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -44206,10 +44367,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -44222,14 +44385,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -44238,14 +44404,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -44264,26 +44433,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -44302,6 +44477,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -44310,10 +44486,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -44322,6 +44500,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -44334,10 +44513,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -44346,6 +44527,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -44354,14 +44536,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -44370,14 +44555,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -44394,76 +44582,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -44477,31 +44674,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -44514,10 +44718,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -44526,10 +44732,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -44538,6 +44746,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -44552,10 +44761,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -44564,10 +44775,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -44581,6 +44794,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -44596,14 +44810,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -44621,14 +44838,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -44641,10 +44861,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -44653,14 +44875,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -44669,10 +44894,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -44681,14 +44908,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -44710,6 +44940,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -44718,39 +44949,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{911E5ED7-BD2D-45D7-8DC4-2B0949C7DCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9920186E-F383-4793-A600-57D4A826F6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -605,7 +605,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -794,7 +794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>30</v>
       </c>
@@ -919,7 +919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>30</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>30</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
@@ -1763,7 +1763,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>30</v>
       </c>
@@ -1963,16 +1963,16 @@
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H48" s="2">
-        <v>0</v>
+        <v>6.145833333333333E-3</v>
       </c>
       <c r="I48" s="1">
         <v>46237.814930555556</v>
       </c>
       <c r="J48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>11</v>
@@ -2031,7 +2031,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H54" s="2"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
@@ -2151,7 +2151,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H74" s="2"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
@@ -2199,7 +2199,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -2259,7 +2259,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
@@ -2379,7 +2379,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -2397,7 +2397,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -2469,7 +2469,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -2751,7 +2751,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -2781,7 +2781,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -2841,7 +2841,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -2949,7 +2949,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -3141,7 +3141,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -3657,7 +3657,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -3723,7 +3723,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -3735,7 +3735,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -3831,7 +3831,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -3843,7 +3843,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -3939,7 +3939,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -3999,7 +3999,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -42952,6 +42952,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43244,6 +43245,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -43554,6 +43557,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -43678,6 +43682,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -43689,6 +43694,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -43837,6 +43843,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -43847,10 +43854,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -43884,15 +43893,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -43933,18 +43945,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -43960,6 +43976,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -43969,10 +43986,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -44008,10 +44027,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -44037,6 +44058,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -44051,6 +44073,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44085,6 +44108,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -44094,6 +44118,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -44103,6 +44128,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -44117,15 +44143,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -44155,6 +44182,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44175,11 +44203,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -44188,6 +44218,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -44217,6 +44248,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -44226,10 +44258,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -44244,14 +44278,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -44271,10 +44308,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -44294,9 +44333,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -44331,18 +44373,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44357,12 +44403,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -44377,10 +44423,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -44400,6 +44448,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -44419,6 +44468,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44428,6 +44478,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -44473,6 +44524,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -44482,6 +44534,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -44496,6 +44549,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -44505,10 +44559,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -44523,6 +44579,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -44532,6 +44589,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -44551,6 +44609,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -44570,10 +44629,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -44583,6 +44644,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -44593,10 +44655,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -44611,18 +44675,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -44642,10 +44710,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -44665,6 +44735,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -44695,7 +44766,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -44710,10 +44780,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -44728,6 +44800,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -44742,11 +44815,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -44756,6 +44829,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -44771,6 +44845,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -44785,6 +44860,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -44805,6 +44881,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -44830,11 +44907,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -44853,15 +44932,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -44871,6 +44951,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -44890,6 +44971,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -44904,6 +44986,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -44923,10 +45006,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -44936,6 +45021,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -44946,6 +45032,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -44982,7 +45069,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -44991,6 +45077,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -45004,10 +45091,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9920186E-F383-4793-A600-57D4A826F6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C7266BB-8011-4F60-B0A4-617AE42AB3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -605,7 +605,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -794,7 +794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>30</v>
       </c>
@@ -919,7 +919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>30</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>30</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
@@ -1763,7 +1763,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>30</v>
       </c>
@@ -2031,7 +2031,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H54" s="2"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
@@ -2151,7 +2151,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H74" s="2"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
@@ -2199,7 +2199,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -2259,7 +2259,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
@@ -2379,7 +2379,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -2397,7 +2397,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -2469,7 +2469,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -2751,7 +2751,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -2781,7 +2781,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -2841,7 +2841,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -2949,7 +2949,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -3141,7 +3141,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -3657,7 +3657,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -3723,7 +3723,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -3735,7 +3735,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -3831,7 +3831,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -3843,7 +3843,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -3939,7 +3939,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -3999,7 +3999,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -42952,7 +42952,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43245,8 +43244,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -43557,7 +43554,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -43682,7 +43678,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -43694,7 +43689,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -43843,35 +43837,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -43882,44 +43870,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -43930,37 +43909,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -43971,52 +43943,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -44027,17 +43989,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -44048,32 +44007,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44083,106 +44036,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44192,7 +44125,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44203,127 +44135,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44333,62 +44239,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44408,67 +44301,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44478,38 +44358,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -44524,117 +44397,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -44643,99 +44493,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -44745,23 +44576,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -44770,52 +44597,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -44829,38 +44646,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -44870,7 +44680,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -44881,23 +44690,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -44907,37 +44712,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -44946,72 +44744,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -45021,76 +44805,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C7266BB-8011-4F60-B0A4-617AE42AB3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46A788A2-96BC-41A8-AD11-933AEFBD94E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -42952,6 +42952,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43244,6 +43245,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -43554,6 +43557,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -43678,6 +43682,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -43689,6 +43694,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -43837,29 +43843,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -43870,35 +43882,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -43909,30 +43930,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -43943,42 +43971,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -43989,14 +44027,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -44007,26 +44048,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44036,86 +44083,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44125,6 +44193,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44135,101 +44204,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44239,49 +44334,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44296,59 +44404,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44358,31 +44480,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -44392,99 +44521,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -44493,80 +44646,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -44576,67 +44748,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -44646,31 +44834,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -44680,6 +44875,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -44690,19 +44886,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -44712,90 +44912,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -44805,51 +45027,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
